--- a/e-codices/e-codices.xlsx
+++ b/e-codices/e-codices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HeimK\switchdrive\dlza\dlza\e-codices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F5C030-D620-496A-AD2F-72827409B58A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42598114-2BEC-4D84-9626-064B45263E8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -397,64 +397,64 @@
     <t>Anfang des 13. Jahrhunderts</t>
   </si>
   <si>
-    <t>9914249443205505x</t>
-  </si>
-  <si>
-    <t>9914249441205505x</t>
-  </si>
-  <si>
-    <t>9914249440305505x</t>
-  </si>
-  <si>
-    <t>9914249439505505x</t>
-  </si>
-  <si>
-    <t>9914249439005505x</t>
-  </si>
-  <si>
-    <t>9914249437805505x</t>
-  </si>
-  <si>
-    <t>9914249437605505x</t>
-  </si>
-  <si>
-    <t>9914249437405505x</t>
-  </si>
-  <si>
-    <t>9914249436205505x</t>
-  </si>
-  <si>
-    <t>9914249426405505x</t>
-  </si>
-  <si>
-    <t>9914249425905505x</t>
-  </si>
-  <si>
-    <t>9914249424805505x</t>
-  </si>
-  <si>
-    <t>9914249424605505x</t>
-  </si>
-  <si>
-    <t>9914249423805505x</t>
-  </si>
-  <si>
-    <t>9914249329905505x</t>
-  </si>
-  <si>
-    <t>9914249303805505x</t>
-  </si>
-  <si>
-    <t>9914249300405505x</t>
-  </si>
-  <si>
-    <t>9914249327205505x</t>
-  </si>
-  <si>
-    <t>9914249325605505x</t>
-  </si>
-  <si>
-    <t>9914249327405505x</t>
+    <t>9914249443205505</t>
+  </si>
+  <si>
+    <t>9914249441205505</t>
+  </si>
+  <si>
+    <t>9914249440305505</t>
+  </si>
+  <si>
+    <t>9914249439505505</t>
+  </si>
+  <si>
+    <t>9914249439005505</t>
+  </si>
+  <si>
+    <t>9914249437805505</t>
+  </si>
+  <si>
+    <t>9914249437605505</t>
+  </si>
+  <si>
+    <t>9914249437405505</t>
+  </si>
+  <si>
+    <t>9914249436205505</t>
+  </si>
+  <si>
+    <t>9914249426405505</t>
+  </si>
+  <si>
+    <t>9914249425905505</t>
+  </si>
+  <si>
+    <t>9914249424805505</t>
+  </si>
+  <si>
+    <t>9914249424605505</t>
+  </si>
+  <si>
+    <t>9914249423805505</t>
+  </si>
+  <si>
+    <t>9914249329905505</t>
+  </si>
+  <si>
+    <t>9914249303805505</t>
+  </si>
+  <si>
+    <t>9914249300405505</t>
+  </si>
+  <si>
+    <t>9914249327205505</t>
+  </si>
+  <si>
+    <t>9914249325605505</t>
+  </si>
+  <si>
+    <t>9914249327405505</t>
   </si>
 </sst>
 </file>
@@ -944,7 +944,7 @@
       <c r="D2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>124</v>
       </c>
       <c r="F2" t="s">
@@ -968,7 +968,7 @@
       <c r="D3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>125</v>
       </c>
       <c r="F3" t="s">
@@ -991,7 +991,7 @@
       <c r="D4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>126</v>
       </c>
       <c r="F4" t="s">
@@ -1014,7 +1014,7 @@
       <c r="D5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>127</v>
       </c>
       <c r="F5" t="s">
@@ -1037,7 +1037,7 @@
       <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>128</v>
       </c>
       <c r="F6" t="s">
@@ -1060,7 +1060,7 @@
       <c r="D7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>129</v>
       </c>
       <c r="F7" t="s">
@@ -1083,7 +1083,7 @@
       <c r="D8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>130</v>
       </c>
       <c r="F8" t="s">
@@ -1106,7 +1106,7 @@
       <c r="D9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>131</v>
       </c>
       <c r="F9" t="s">
@@ -1129,7 +1129,7 @@
       <c r="D10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>132</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -1153,7 +1153,7 @@
       <c r="D11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F11" t="s">
@@ -1176,7 +1176,7 @@
       <c r="D12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F12" t="s">
@@ -1199,7 +1199,7 @@
       <c r="D13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F13" t="s">
@@ -1222,7 +1222,7 @@
       <c r="D14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>136</v>
       </c>
       <c r="F14" t="s">
@@ -1245,7 +1245,7 @@
       <c r="D15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>137</v>
       </c>
       <c r="F15" t="s">
@@ -1268,7 +1268,7 @@
       <c r="D16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F16" t="s">
@@ -1291,7 +1291,7 @@
       <c r="D17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F17" t="s">
@@ -1314,7 +1314,7 @@
       <c r="D18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>140</v>
       </c>
       <c r="F18" t="s">
@@ -1338,7 +1338,7 @@
       <c r="D19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>141</v>
       </c>
       <c r="F19" t="s">
@@ -1361,7 +1361,7 @@
       <c r="D20" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>142</v>
       </c>
       <c r="F20" t="s">
@@ -1400,6 +1400,9 @@
   </sheetData>
   <autoFilter ref="A1:H21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="E2:E21" numberStoredAsText="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/e-codices/e-codices.xlsx
+++ b/e-codices/e-codices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HeimK\switchdrive\dlza\dlza\e-codices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42598114-2BEC-4D84-9626-064B45263E8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FD5F6D-1E2F-48F6-A5BC-902AE6FEA935}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="results" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">results!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">results!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>Title</t>
   </si>
@@ -154,9 +154,6 @@
     <t>(HAN)000190001DSV05</t>
   </si>
   <si>
-    <t>Created</t>
-  </si>
-  <si>
     <t>Msc.34.4</t>
   </si>
   <si>
@@ -344,57 +341,6 @@
   </si>
   <si>
     <t>DOI</t>
-  </si>
-  <si>
-    <t>1402.12.17.-1411.10.28.</t>
-  </si>
-  <si>
-    <t>1461.05.12.-1461.07.31.</t>
-  </si>
-  <si>
-    <t>1459.12.04-1461.09.20</t>
-  </si>
-  <si>
-    <t>1460-1462</t>
-  </si>
-  <si>
-    <t>1460.07.06.-1462.05.06.</t>
-  </si>
-  <si>
-    <t>1460.03.0.7-1461.03.05.</t>
-  </si>
-  <si>
-    <t>1460.01.05-1461.10.09</t>
-  </si>
-  <si>
-    <t>[Oberrhein, Region] 1338–1340</t>
-  </si>
-  <si>
-    <t>Prag um 1410</t>
-  </si>
-  <si>
-    <t>[Oberrhein, Region] 1338</t>
-  </si>
-  <si>
-    <t>St. Urban 1. Viertel 13. Jh.</t>
-  </si>
-  <si>
-    <t>1340, 1339</t>
-  </si>
-  <si>
-    <t>Paris Ende des 15. Jahrhunderts</t>
-  </si>
-  <si>
-    <t>Basel 25. November 1516 [Teil 1], 5. März 1517 [Teil 2]</t>
-  </si>
-  <si>
-    <t>2. Hälfte 12. Jh.</t>
-  </si>
-  <si>
-    <t>um 1200</t>
-  </si>
-  <si>
-    <t>Anfang des 13. Jahrhunderts</t>
   </si>
   <si>
     <t>9914249443205505</t>
@@ -553,7 +499,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>946150</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>825500</xdr:rowOff>
     </xdr:to>
@@ -893,515 +839,451 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.453125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="68.7265625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.36328125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="40.08984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.36328125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="71.81640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="35.36328125" customWidth="1"/>
-    <col min="8" max="8" width="51.08984375" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="1" width="68.7265625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="40.08984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.36328125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="71.81640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="35.36328125" customWidth="1"/>
+    <col min="7" max="7" width="51.08984375" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="D2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="F2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="E3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="E20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
-        <v>1459</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
-        <v>1513</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F14" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F15" t="s">
-        <v>79</v>
-      </c>
-      <c r="G15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E21" t="s">
         <v>80</v>
       </c>
-      <c r="G16" t="s">
+      <c r="F21" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>1453</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="F18" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" t="s">
-        <v>105</v>
-      </c>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F19" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="H22" s="6"/>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G22" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E2:E21" numberStoredAsText="1"/>
+    <ignoredError sqref="D2:D21" numberStoredAsText="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
